--- a/resources/templates/standard/B1100-10.xlsx
+++ b/resources/templates/standard/B1100-10.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>폐기보고 관리대장</t>
   </si>
@@ -604,12 +607,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -757,36 +762,36 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
       <c r="T4" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
@@ -811,12 +816,12 @@
       <c r="AO4" s="6"/>
       <c r="AP4" s="6"/>
       <c r="AQ4" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR4" s="6"/>
       <c r="AS4" s="6"/>
       <c r="AT4" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU4" s="6"/>
       <c r="AV4" s="6"/>
@@ -842,7 +847,7 @@
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
       <c r="T5" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U5" s="7"/>
       <c r="V5" s="7"/>
@@ -851,18 +856,18 @@
       <c r="Y5" s="7"/>
       <c r="Z5" s="7"/>
       <c r="AA5" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB5" s="7"/>
       <c r="AC5" s="7"/>
       <c r="AD5" s="7"/>
       <c r="AE5" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF5" s="7"/>
       <c r="AG5" s="7"/>
       <c r="AH5" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI5" s="7"/>
       <c r="AJ5" s="7"/>
@@ -870,7 +875,7 @@
       <c r="AL5" s="7"/>
       <c r="AM5" s="7"/>
       <c r="AN5" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO5" s="7"/>
       <c r="AP5" s="7"/>
@@ -1483,7 +1488,7 @@
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
